--- a/output/full_scan/batch_seq0_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-19.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>855.5658450458002</v>
+        <v>1055.565845045802</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>61.1</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.95785967968949</v>
+        <v>63.95785975793948</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.92271401124029</v>
+        <v>22.92271402618447</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.102439539091279</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5555917727926958</v>
+        <v>0.555591772612438</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8358</v>
+        <v>8213</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>848.7944654853845</v>
+        <v>1044.12044456763</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>484</v>
+        <v>38.9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46.84009509674637</v>
+        <v>66.74906048452472</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>22.91658317993637</v>
+        <v>46.50902906395376</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.731202172944487</v>
+        <v>0.7011953269986284</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-8.102337644508646</v>
+        <v>0.3969579521958555</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8213</v>
+        <v>8429</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>794.1204445676298</v>
+        <v>969.7341094123096</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>38.9</v>
+        <v>6.22</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.74906035488121</v>
+        <v>77.04064225519942</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46.50902902863032</v>
+        <v>11.31681951539354</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.7011953269986284</v>
+        <v>5.521382460062609</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3969579522799809</v>
+        <v>0.0255687394232916</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8429</v>
+        <v>8046</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>769.7341094123099</v>
+        <v>959.6279380701041</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.22</v>
+        <v>1380</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>77.04064228295225</v>
+        <v>57.18754578478486</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11.31681940045131</v>
+        <v>25.25437322883333</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.521382460062609</v>
+        <v>0.6937138684436891</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0255687394112736</v>
+        <v>-8.870942333567754</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8240</v>
+        <v>9105</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>753.8222492134945</v>
+        <v>918.937491422495</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>50.2</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>44.02822843662466</v>
+        <v>58.75398461641313</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.44951784257172</v>
+        <v>29.71786922811556</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2151127485494262</v>
+        <v>1.460447756624228</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.9819402244072966</v>
+        <v>0.0680969568904039</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8046</v>
+        <v>8089</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>729.4482464842108</v>
+        <v>918.3541137425392</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1380</v>
+        <v>23.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.18754575887783</v>
+        <v>76.78754314365828</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.25437321667158</v>
+        <v>40.56466382608712</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6796348648769329</v>
+        <v>4.935411374253919</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-8.870942333808102</v>
+        <v>0.3261137759827538</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8089</v>
+        <v>8050</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>718.3541137425392</v>
+        <v>886.2678117653314</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>23.8</v>
+        <v>64.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>76.78754310737251</v>
+        <v>58.56953830723317</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.56466380110423</v>
+        <v>32.23100089670594</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.935411374253919</v>
+        <v>0.44521660184897</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3261137757904737</v>
+        <v>0.2720149823911566</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8289</v>
+        <v>8367</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>712.0470926864675</v>
+        <v>852.536461453789</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>50.5</v>
+        <v>41.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>48.93435281305553</v>
+        <v>57.97793764161348</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>34.34697314308455</v>
+        <v>17.00150502924691</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3345867957740454</v>
+        <v>0.1865272441413699</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.2340568691898372</v>
+        <v>0.0764061868885174</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8050</v>
+        <v>8358</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>686.2678117653314</v>
+        <v>848.7944654853844</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>64.3</v>
+        <v>484</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.5695382267176</v>
+        <v>46.84009506249971</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>32.23100089670594</v>
+        <v>22.91658309540841</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.44521660184897</v>
+        <v>1.731202172944487</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2720149823190496</v>
+        <v>-8.102337641504365</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9105</v>
+        <v>8069</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>683.9374914224948</v>
+        <v>815.8469407636192</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>157</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,29 +1029,29 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.75398458779213</v>
+        <v>58.81355236998849</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>29.71786940066447</v>
+        <v>23.40310825001375</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.460447756624228</v>
+        <v>1.297641036161083</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0680969568976145</v>
+        <v>1.982839118719449</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>666.0268543280533</v>
+        <v>781.0268543280533</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>102.5</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44.38753558362902</v>
+        <v>44.38753559407911</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.65959627418801</v>
+        <v>33.65959630472363</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.2369118693842924</v>
@@ -1094,37 +1094,37 @@
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-2.561784594300935</v>
+        <v>-2.561784594288917</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8069</v>
+        <v>8070</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>615.8469407636193</v>
+        <v>776.0639474276898</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>157</v>
+        <v>51.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.81355254687386</v>
+        <v>52.23550049734519</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.40310771187463</v>
+        <v>19.8892984015335</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.297641036161083</v>
+        <v>0.5046260667578868</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>1</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.982839115114248</v>
+        <v>0.0720181257397248</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>604.9794880933579</v>
+        <v>774.979488093358</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>67.5</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.46283529453168</v>
+        <v>58.46283531075682</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.30203586474353</v>
+        <v>30.30203583468727</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.236189673333387</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0603038746725408</v>
+        <v>0.0603038746004318</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8367</v>
+        <v>8240</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>602.536461453789</v>
+        <v>753.8222492134945</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>41.5</v>
+        <v>50.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.97793769887448</v>
+        <v>44.02822847513332</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.00150503700279</v>
+        <v>27.44951785316339</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.1865272441413699</v>
+        <v>0.2151127485494262</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0764061868885174</v>
+        <v>-0.9819402242630844</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8996</v>
+        <v>8462</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>596.637214032584</v>
+        <v>726.6594055672749</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1525</v>
+        <v>158</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.12710435649505</v>
+        <v>47.20791096806385</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>40.55417141194467</v>
+        <v>35.18340611501344</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.173395893762886</v>
+        <v>1.795410065877117</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-20.71927758931768</v>
+        <v>0.3741162252263055</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8040</v>
+        <v>8422</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>574.5861509418745</v>
+        <v>719.4138115731485</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>82.5</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45.11348850687095</v>
+        <v>53.84811867403579</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.51962518903917</v>
+        <v>9.703366671651825</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2289787336498114</v>
+        <v>2.302358321175465</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.744276535119435</v>
+        <v>0.0631041785526831</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8042</v>
+        <v>8289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>552.5227147315354</v>
+        <v>712.0470926864675</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>131</v>
+        <v>50.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>53.01575650169885</v>
+        <v>48.93435281305553</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40.92577749041433</v>
+        <v>34.34697325505914</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6365050397347176</v>
+        <v>0.3345867957740454</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.812930867432902</v>
+        <v>-0.2340568692018578</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8182</v>
+        <v>8996</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>548.3895510823097</v>
+        <v>711.637214032584</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39</v>
+        <v>1525</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>43.30779337726634</v>
+        <v>51.12710436525318</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.99614061818735</v>
+        <v>40.55417140463946</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2165611558647282</v>
+        <v>1.173395893762886</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.4816262145332125</v>
+        <v>-20.71927759100012</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8171</v>
+        <v>8081</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>547.7620026753577</v>
+        <v>703.8002091853552</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21.9</v>
+        <v>261</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.94511692049729</v>
+        <v>52.64631427479146</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.22449030522725</v>
+        <v>17.52068115151512</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8778701298701299</v>
+        <v>1.37305493033934</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0968218620538434</v>
+        <v>0.8923418127240028</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8442</v>
+        <v>8454</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>547.0482049984422</v>
+        <v>698.3849049861163</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>48.2</v>
+        <v>249.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.34982244640618</v>
+        <v>54.53123973778155</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.14372257800569</v>
+        <v>14.10814281528792</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4487971492221899</v>
+        <v>0.8178218861055173</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.2412566727346335</v>
+        <v>1.79598923204327</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8086</v>
+        <v>8171</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>527.3206061262003</v>
+        <v>687.7620026753577</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>129.5</v>
+        <v>21.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.66154368103831</v>
+        <v>61.9451169448237</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.90625209631627</v>
+        <v>30.224490205115</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4813206524020293</v>
+        <v>0.8778701298701299</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4266139949257512</v>
+        <v>0.09682186200577519</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8070</v>
+        <v>8442</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>526.0639474276875</v>
+        <v>687.0482049984421</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.23550051078321</v>
+        <v>61.34982276787213</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.8892984136955</v>
+        <v>20.1437226027668</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5046260667578868</v>
+        <v>0.4487971492221899</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0720181256556091</v>
+        <v>0.2412566728548069</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8201</v>
+        <v>8215</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>521.4804322455352</v>
+        <v>670.3835113554284</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>14.2</v>
+        <v>27.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>47.65871353958687</v>
+        <v>52.72753187675497</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>43.94439536032509</v>
+        <v>32.19725851529628</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4747518535419451</v>
+        <v>0.2428952985577505</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2611743787217295</v>
+        <v>-0.1759627021846893</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8112</v>
+        <v>8044</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>514.4274434305615</v>
+        <v>658.2491659137622</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>41.23041009620427</v>
+        <v>56.47351806435335</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.90660039705255</v>
+        <v>26.18250512713009</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.936568208632657</v>
+        <v>0.7555157732498169</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,51 +1789,51 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.2098765591912832</v>
+        <v>0.2633721726438593</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8908</v>
+        <v>8940</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>500.8642278537412</v>
+        <v>632.1494638316078</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>40.2</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.97361631453582</v>
+        <v>53.57404390303127</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.22478438736653</v>
+        <v>12.5944355735213</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.760617295114085</v>
+        <v>0.7593077190893878</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0055654508664575</v>
+        <v>0.0249975106782512</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8093</v>
+        <v>8201</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>491.0147956057006</v>
+        <v>631.4804322455352</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>27.2</v>
+        <v>14.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.33214064858779</v>
+        <v>47.65871332497612</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14.82329727404104</v>
+        <v>43.94439595340488</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.262287937680386</v>
+        <v>0.4747518535419451</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1653333252954224</v>
+        <v>-0.2611743784453333</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8215</v>
+        <v>8093</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>480.3835113554283</v>
+        <v>631.0147956057007</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.72753178967641</v>
+        <v>55.33214065794101</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.19725849116642</v>
+        <v>14.82329728441698</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2428952985577505</v>
+        <v>0.262287937680386</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.1759627020284621</v>
+        <v>0.1653333252542327</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8227</v>
+        <v>8112</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>476.6890870022477</v>
+        <v>629.4274434305615</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>277.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>47.04017203524335</v>
+        <v>41.23041012485498</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.46286819629865</v>
+        <v>14.90660040690411</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9172851714702218</v>
+        <v>0.936568208632657</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-13.7537947217959</v>
+        <v>0.2098765592513637</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8038</v>
+        <v>8277</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>465.6782945195188</v>
+        <v>610.2914642654549</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>34</v>
+        <v>15.45</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.97984375577028</v>
+        <v>75.73333486691504</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>29.25032608791194</v>
+        <v>37.55908995581839</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6721034508168674</v>
+        <v>0.6799593074692012</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0606112998042179</v>
+        <v>-0.1955668825471659</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8096</v>
+        <v>8383</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>465.5241044095296</v>
+        <v>602.7839948879124</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>37.39283703065371</v>
+        <v>53.69030232486018</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.42423689315509</v>
+        <v>17.20895249222881</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8515595081755603</v>
+        <v>0.6279235769607077</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>2</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6780548605971033</v>
+        <v>0.0525558406862023</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8044</v>
+        <v>8423</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>458.2491659137614</v>
+        <v>597.5558199020081</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.3</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.4735179754581</v>
+        <v>51.72496049245999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.18250507931045</v>
+        <v>27.87953458003351</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7555157732498169</v>
+        <v>4.494877872717312</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2633721727640287</v>
+        <v>0.0081955656306964</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8081</v>
+        <v>8109</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>448.8002091853552</v>
+        <v>588.5488577981558</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>261</v>
+        <v>133</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.64631421279165</v>
+        <v>48.24483559349905</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.52068115751695</v>
+        <v>21.70040208543861</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.37305493033934</v>
+        <v>0.5022211231875214</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.8923418127240028</v>
+        <v>-0.5876424233251776</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8109</v>
+        <v>8096</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>448.5488577981558</v>
+        <v>580.5241044095296</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>133</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.24483535342516</v>
+        <v>37.39283701201506</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.70040210357072</v>
+        <v>30.42423691950595</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5022211231875214</v>
+        <v>0.8515595081755603</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.5876424230608035</v>
+        <v>0.67805486068122</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8462</v>
+        <v>8464</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>446.659405567275</v>
+        <v>578.7538321892184</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>158</v>
+        <v>361.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.20791092285334</v>
+        <v>43.06312929808167</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>35.18340600560202</v>
+        <v>10.2383677710814</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.795410065877117</v>
+        <v>2.249404784867046</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3741162243850926</v>
+        <v>-0.1371028160754764</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8277</v>
+        <v>8040</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>440.2914642654549</v>
+        <v>574.5861509418745</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15.45</v>
+        <v>82.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>75.73333489395927</v>
+        <v>45.11348852176697</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.55908987617318</v>
+        <v>21.51962520487967</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6799593074692012</v>
+        <v>0.2289787336498114</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1955668825471659</v>
+        <v>-1.744276535095399</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8162</v>
+        <v>9912</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>433.0944945487687</v>
+        <v>571.7206774749353</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>59.6</v>
+        <v>13.15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.01965764829426</v>
+        <v>52.19340232303633</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.77874319655709</v>
+        <v>27.69826766704641</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3835205441634375</v>
+        <v>2.177449078457467</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.7804936211721768</v>
+        <v>0.1379678342070907</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8383</v>
+        <v>9110</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>432.7839948879123</v>
+        <v>562.7659377558813</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>3.03</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.69030241303915</v>
+        <v>51.70130289121784</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.20895249162201</v>
+        <v>4.695316047628306</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6279235769607077</v>
+        <v>1.283083990696078</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0525558403016552</v>
+        <v>-0.0122271498450153</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8068</v>
+        <v>9930</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>430.8770328943152</v>
+        <v>562.7487889874792</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>17.7</v>
+        <v>58.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.68829486227379</v>
+        <v>33.44688485613426</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>33.24360827402512</v>
+        <v>29.92811218158709</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5482438162244214</v>
+        <v>1.979705780469339</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0170979823551435</v>
+        <v>0.0572216180852918</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8476</v>
+        <v>8097</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>430.3150511428635</v>
+        <v>560.5894334887433</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>20.65</v>
+        <v>48.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.66191543236314</v>
+        <v>44.73183446525277</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.86401619057224</v>
+        <v>14.5339671585985</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.41586765363406</v>
+        <v>0.2775319460277425</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0824934243874976</v>
+        <v>0.0539687069827984</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8422</v>
+        <v>8042</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>429.4138115731486</v>
+        <v>552.5227147315354</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.84811941151309</v>
+        <v>53.01575652352216</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9.703366671651819</v>
+        <v>40.92577748274027</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.302358321175465</v>
+        <v>0.6365050397347176</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0631041777288576</v>
+        <v>1.812930867324738</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8423</v>
+        <v>8249</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>427.5558199020081</v>
+        <v>551.116433388945</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>18</v>
+        <v>39.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.72496046176678</v>
+        <v>48.08023419553111</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.87953455133428</v>
+        <v>13.26879048520739</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.494877872717312</v>
+        <v>0.7083906143006886</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0081955656427145</v>
+        <v>0.09468829024009839</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>9110</v>
+        <v>8039</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>422.7659377558811</v>
+        <v>550.291055116311</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>3.03</v>
+        <v>299</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.70130289704935</v>
+        <v>53.28332241061833</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>4.69531580892728</v>
+        <v>20.87749644770666</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.283083990696078</v>
+        <v>2.731854625933634</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0122271498498217</v>
+        <v>0.5390052057613346</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8454</v>
+        <v>8182</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>418.3849049861163</v>
+        <v>548.3895510823097</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>249.5</v>
+        <v>39</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.53123977180849</v>
+        <v>43.30779338131133</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.10814285266671</v>
+        <v>21.99614063012864</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8178218861055173</v>
+        <v>0.2165611558647282</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.795989231802868</v>
+        <v>-0.4816262145572456</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8103</v>
+        <v>8440</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>413.6926926834804</v>
+        <v>545.6076457693953</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>103.5</v>
+        <v>19.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>38.65647659275967</v>
+        <v>42.4530221229739</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.38652903072504</v>
+        <v>21.7220395425201</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2356608407297304</v>
+        <v>1.143157304815129</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-2.746006183243174</v>
+        <v>-0.0358485030048651</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8299</v>
+        <v>8476</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>408.0732137013436</v>
+        <v>545.3150511428638</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1845</v>
+        <v>20.65</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>34.53554699269149</v>
+        <v>52.66191537683805</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.89678956675944</v>
+        <v>28.86401619585469</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7215894511644727</v>
+        <v>1.41586765363406</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-30.34872239321045</v>
+        <v>0.0824934244115339</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8440</v>
+        <v>8463</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>405.6076457693952</v>
+        <v>543.9460141223611</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>19.85</v>
+        <v>21.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.45302197517407</v>
+        <v>51.52725186246597</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.72203953510666</v>
+        <v>24.84999574419584</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.143157304815129</v>
+        <v>0.4618793496239428</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.035848502992848</v>
+        <v>0.0213202551144381</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8147</v>
+        <v>8086</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>402.6519199594031</v>
+        <v>527.3206061262003</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>42.80808573756838</v>
+        <v>53.66154363107115</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.45469017716787</v>
+        <v>27.9062521397573</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6218494888759204</v>
+        <v>0.4813206524020293</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.888431515397048</v>
+        <v>0.4266139952862735</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8210</v>
+        <v>8488</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>398.3794775590271</v>
+        <v>521.336956798953</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>813</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>33.62749932660982</v>
+        <v>51.28385663689367</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.53459392669601</v>
+        <v>27.32552112576579</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6882830172895114</v>
+        <v>0.0192516560434959</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0983440546445386</v>
+        <v>0.1183175242664105</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8482</v>
+        <v>8045</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>392.4601324954146</v>
+        <v>517.6849699506855</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>48.95</v>
+        <v>54.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.60245008054738</v>
+        <v>50.83867191623526</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6.092236870480767</v>
+        <v>20.76898473410026</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1661080249083905</v>
+        <v>0.5591389190622782</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0339767607389646</v>
+        <v>0.0124593953231176</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8455</v>
+        <v>8467</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>390.7895499762977</v>
+        <v>515.9970015136939</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>23.7</v>
+        <v>99</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.91301299927999</v>
+        <v>56.26793338532055</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9.427735313435148</v>
+        <v>16.9456089581845</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.783184441920641</v>
+        <v>0.4914043153129372</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.44463528390033</v>
+        <v>1.659846986442276</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8097</v>
+        <v>8482</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>390.5894334887435</v>
+        <v>507.4601324954146</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.4</v>
+        <v>48.95</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.73183422645664</v>
+        <v>50.60245003069762</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.53396712964128</v>
+        <v>6.092236821939236</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2775319460277425</v>
+        <v>0.1661080249083905</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,51 +3220,51 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0539687072712202</v>
+        <v>0.0339767606908953</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8271</v>
+        <v>8908</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>383.8573071761579</v>
+        <v>500.8642278537412</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>181.5</v>
+        <v>40.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29.49666099299654</v>
+        <v>53.9736162397655</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.7962121748358</v>
+        <v>15.22478439187398</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7882018789516083</v>
+        <v>0.760617295114085</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.259271515022562</v>
+        <v>-0.0055654508794357</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8940</v>
+        <v>8341</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>382.149463831608</v>
+        <v>494.7700762079758</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.57404380730127</v>
+        <v>48.57303483612235</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.59443556126628</v>
+        <v>12.49285210353396</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7593077190893878</v>
+        <v>1.969761977587104</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0249975107022837</v>
+        <v>0.1085993931428757</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8045</v>
+        <v>8176</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>377.6849699506857</v>
+        <v>491.9255244295051</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>54.5</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.83867184567935</v>
+        <v>51.80783517974571</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.76898469310218</v>
+        <v>20.95803857783542</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5591389190622782</v>
+        <v>0.8491118055409912</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,11 +3379,11 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0124593949625992</v>
+        <v>0.007924396826451401</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>374.3810229465657</v>
+        <v>489.3810229465657</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>57.2</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.83993955553655</v>
+        <v>41.83993949531505</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.41275314791953</v>
+        <v>13.41275311160877</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.310032733234814</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1410017349069942</v>
+        <v>-0.1410017348589164</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8064</v>
+        <v>8155</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>373.6321740034868</v>
+        <v>483.4827688993944</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>117</v>
+        <v>304</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>41.49927350759163</v>
+        <v>40.93023899510619</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.32579698160819</v>
+        <v>13.68174691034902</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2683204931530223</v>
+        <v>0.7321618504281842</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-3.346325048072868</v>
+        <v>-2.426662248465202</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>9912</v>
+        <v>8227</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>371.7206774749353</v>
+        <v>476.6890870022477</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13.15</v>
+        <v>277.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.19340232083593</v>
+        <v>47.04017209772979</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.69826763009186</v>
+        <v>35.46286823928246</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.177449078457467</v>
+        <v>0.9172851714702218</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1379678342431433</v>
+        <v>-13.75379472059416</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, adx_trending, breakout_volume_confirm</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8059</v>
+        <v>8091</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>371.4367407824298</v>
+        <v>474.3750291543441</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>17</v>
+        <v>208.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.25875319146482</v>
+        <v>40.48846054779839</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.70310539748249</v>
+        <v>15.90983121496574</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3084563983674891</v>
+        <v>0.8485581834140851</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1399013842003352</v>
+        <v>-1.787928320876718</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8438</v>
+        <v>8038</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>370.3499115629829</v>
+        <v>465.6782945195184</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>34</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.89557306593418</v>
+        <v>51.97984369424017</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>27.19622579429839</v>
+        <v>29.25032603932818</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5425143981991288</v>
+        <v>0.6721034508168674</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,51 +3644,51 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.245556209954237</v>
+        <v>-0.0606113003570163</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8047</v>
+        <v>8114</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>369.6497012691831</v>
+        <v>458.2905814581497</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>44.4</v>
+        <v>177</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.18577418312818</v>
+        <v>42.20338951328742</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7.474352711877317</v>
+        <v>17.50859654203739</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6480589829337459</v>
+        <v>0.944629135766388</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0039183410495979</v>
+        <v>0.9394566155943118</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8155</v>
+        <v>8087</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>368.4827688993944</v>
+        <v>438.7103008587856</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>304</v>
+        <v>22</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.93023901851068</v>
+        <v>45.63568800621151</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.68174702507197</v>
+        <v>4.454857736222685</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7321618504281842</v>
+        <v>0.6145964851176223</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.426662249426577</v>
+        <v>-0.06744434157159079</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8110</v>
+        <v>8162</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>364.7919809303621</v>
+        <v>433.0944945487687</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46.3</v>
+        <v>59.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.09912376808955</v>
+        <v>41.01965767138283</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.33506594662498</v>
+        <v>19.77874320031933</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.223909071067914</v>
+        <v>0.3835205441634375</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.4196498802439607</v>
+        <v>-0.7804936211361321</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8039</v>
+        <v>8068</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>360.291055116311</v>
+        <v>430.8770328943152</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>299</v>
+        <v>17.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.28332240854848</v>
+        <v>49.68829509257263</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.87749643165479</v>
+        <v>33.24360825053016</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.731854625933634</v>
+        <v>0.5482438162244214</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5390052057372916</v>
+        <v>0.0170979822469868</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8091</v>
+        <v>8234</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>359.3750291543444</v>
+        <v>429.5317057338594</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>208.5</v>
+        <v>62.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.48846044805445</v>
+        <v>45.10945661966078</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.90983121496574</v>
+        <v>14.83175522801823</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8485581834140851</v>
+        <v>0.8173012238452428</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.787928320996842</v>
+        <v>0.1830938899032593</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8464</v>
+        <v>8102</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>358.9473191458228</v>
+        <v>424.1757642350469</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>361.5</v>
+        <v>57.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.06312921502496</v>
+        <v>49.65162282209182</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10.23836774940169</v>
+        <v>3.579344396116221</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.537170908906889</v>
+        <v>1.353760520584044</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,48 +3962,48 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.1371028151141116</v>
+        <v>0.5877519525569894</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8183</v>
+        <v>8472</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>355.8634049635203</v>
+        <v>421.7922228221577</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>28.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G67" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.90268875111163</v>
+        <v>54.05239899814286</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.14537608512328</v>
+        <v>28.80296843397732</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>1.699474908288777</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0686206101873692</v>
+        <v>-0.1386467650311094</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8043</v>
+        <v>8443</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>352.6900209675995</v>
+        <v>421.1093246050189</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>134</v>
+        <v>11.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.72880121813821</v>
+        <v>51.81120799023687</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.6895244742315</v>
+        <v>39.44493621920942</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5724287018589082</v>
+        <v>1.092845366576031</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1397509937340862</v>
+        <v>0.1302994445556075</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8131</v>
+        <v>8101</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>335.9961182861014</v>
+        <v>414.6920227075621</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>61.9</v>
+        <v>9.99</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.36081568849968</v>
+        <v>42.12749632373764</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.33396411426864</v>
+        <v>23.62691967095744</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6821088216441075</v>
+        <v>0.8602292035158473</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1249749536904811</v>
+        <v>-0.07581526327796689</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8261</v>
+        <v>8299</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>326.9623959051308</v>
+        <v>408.0732137013436</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>153</v>
+        <v>1845</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>35.52512252327892</v>
+        <v>34.53554699269149</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.90673986003083</v>
+        <v>15.8967895737793</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5853389722790731</v>
+        <v>0.7215894511644727</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-2.996045250626497</v>
+        <v>-30.34872239260957</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8087</v>
+        <v>8103</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>323.7103008587855</v>
+        <v>403.6926926834804</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>22</v>
+        <v>103.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.63568810542831</v>
+        <v>38.65647663849923</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.454857729008608</v>
+        <v>28.38652904977723</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6145964851176223</v>
+        <v>0.2356608407297304</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0674443415235233</v>
+        <v>-2.74600618320198</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8176</v>
+        <v>8147</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>321.9255244295052</v>
+        <v>402.6519199594027</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>129</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.80783545625656</v>
+        <v>42.80808569140734</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.95803853889936</v>
+        <v>26.45469015004058</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8491118055409912</v>
+        <v>0.6218494888759204</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.007924396802417299</v>
+        <v>-1.888431515036539</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8114</v>
+        <v>8477</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>318.2905814581497</v>
+        <v>400.042336085604</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>177</v>
+        <v>13.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.20338929015716</v>
+        <v>34.19826035294805</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.50859656323365</v>
+        <v>37.00016206796385</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.944629135766388</v>
+        <v>0.9738681776825716</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.939456615353964</v>
+        <v>-0.0074195134550766</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8467</v>
+        <v>8466</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>315.9970015136961</v>
+        <v>399.8380929849719</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>56.2679332412481</v>
+        <v>46.79063729851229</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.94560899430824</v>
+        <v>19.39409893746973</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4914043153129372</v>
+        <v>0.3058004692520063</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.659846986802788</v>
+        <v>0.0016823104172243</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8234</v>
+        <v>8210</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>314.5317057338602</v>
+        <v>398.3794775590272</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>62.2</v>
+        <v>813</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.10945703410854</v>
+        <v>33.62749941103644</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.83175489134769</v>
+        <v>22.53459393261637</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8173012238452428</v>
+        <v>0.6882830172895114</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1830938889418757</v>
+        <v>-0.09834405416387069</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8932</v>
+        <v>8049</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>312.8728575111326</v>
+        <v>398.3362639656999</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>24.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.0677610103697</v>
+        <v>35.75227411803994</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.5695391987132</v>
+        <v>13.80531931778297</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8844844895698253</v>
+        <v>1.19875041445949</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0488160076795007</v>
+        <v>-0.0252348739288444</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>9930</v>
+        <v>8455</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>312.7487889874792</v>
+        <v>390.7895499762977</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>58.7</v>
+        <v>23.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>33.44688482408188</v>
+        <v>51.91301298062624</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>29.92811226303507</v>
+        <v>9.427735398299442</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.979705780469339</v>
+        <v>1.783184441920641</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.057221618157396</v>
+        <v>0.4446352841166439</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8102</v>
+        <v>8438</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>309.1757642350466</v>
+        <v>390.3499115629829</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>57.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.65162281776093</v>
+        <v>39.89557307802591</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3.579344459620565</v>
+        <v>27.19622579429839</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.353760520584044</v>
+        <v>0.5425143981991288</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5877519522445243</v>
+        <v>-1.245556209918177</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8121</v>
+        <v>8271</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>305.4277344949398</v>
+        <v>383.8573071761596</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30.15</v>
+        <v>181.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.94950995176836</v>
+        <v>29.4966609881061</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>29.34013310214989</v>
+        <v>22.79621223308437</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3322463420473356</v>
+        <v>0.7882018789516083</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2380532472136092</v>
+        <v>-1.25927151483028</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8249</v>
+        <v>8064</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>301.1164333889367</v>
+        <v>373.6321740034868</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>39.6</v>
+        <v>117</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.08023412934838</v>
+        <v>41.49927351684106</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.26878988140846</v>
+        <v>19.32579701808472</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7083906143006886</v>
+        <v>0.2683204931530223</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0946882905525441</v>
+        <v>-3.34632504792866</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8101</v>
+        <v>8072</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>299.692022707562</v>
+        <v>372.4912065656037</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>9.99</v>
+        <v>26.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.12749624776252</v>
+        <v>38.65441214495493</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.62691961948063</v>
+        <v>26.88344913906675</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8602292035158473</v>
+        <v>0.5229623663093425</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0758152632659494</v>
+        <v>-0.1564944456075118</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8463</v>
+        <v>8059</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>293.946014122361</v>
+        <v>371.4367407824297</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>21.3</v>
+        <v>17</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.52725188851372</v>
+        <v>52.25875332578725</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.84999571885566</v>
+        <v>26.70310542229581</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4618793496239428</v>
+        <v>0.3084563983674891</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0213202550423333</v>
+        <v>-0.1399013843033125</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8411</v>
+        <v>8088</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>283.1774944922904</v>
+        <v>371.2604033611623</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>11.15</v>
+        <v>41.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>22.66303678042379</v>
+        <v>41.19400680540249</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45.90028030377857</v>
+        <v>14.40281624820546</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4483031683734808</v>
+        <v>0.8773492802029538</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,51 +4863,51 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0527370382006971</v>
+        <v>-0.0290883549236897</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8488</v>
+        <v>8047</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.336956798953</v>
+        <v>369.6497012691842</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G84" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.28385527134535</v>
+        <v>50.18577418312818</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>27.32551729038527</v>
+        <v>7.474352812168518</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.0192516560434959</v>
+        <v>0.6480589829337459</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1183175270424079</v>
+        <v>-0.0039183410950121</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8477</v>
+        <v>8084</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>260.0423360856039</v>
+        <v>365.1266038332917</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.19826044779082</v>
+        <v>13.69877086702824</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>37.00016194116027</v>
+        <v>63.71894288367218</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9738681776825716</v>
+        <v>0.2894217607891785</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0074195134791099</v>
+        <v>-0.4476939141659066</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8374</v>
+        <v>8390</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>259.8978557916815</v>
+        <v>364.3868574293143</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>70.5</v>
+        <v>88.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>30.94204873759084</v>
+        <v>38.92355434417945</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.12229763191379</v>
+        <v>17.2197427495942</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.9961367137377904</v>
+        <v>1.142384019663946</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.4197808035930244</v>
+        <v>0.0943728736374458</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8466</v>
+        <v>8085</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>259.8380929849719</v>
+        <v>356.2008846037743</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.79063735947637</v>
+        <v>45.82588156024305</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.39409900592989</v>
+        <v>18.39977401447418</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3058004692520063</v>
+        <v>0.6774960452748267</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,48 +5075,48 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0016823104412584</v>
+        <v>-0.1011007778149604</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8049</v>
+        <v>8183</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>258.3362639656999</v>
+        <v>355.863404963521</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.05</v>
+        <v>28.2</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G88" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>35.75227363164977</v>
+        <v>44.90268885692685</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.80531930581484</v>
+        <v>19.14537613333692</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.19875041445949</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0252348739168267</v>
+        <v>0.06862061064024221</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8088</v>
+        <v>8110</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.2604033611349</v>
+        <v>354.791980930364</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.9</v>
+        <v>46.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.19400687560648</v>
+        <v>47.09912377620038</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.40281624148799</v>
+        <v>22.3350659702741</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8773492802029538</v>
+        <v>0.223909071067914</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.029088355031849</v>
+        <v>-0.419649880207911</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8291</v>
+        <v>8043</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>250.5490675627793</v>
+        <v>352.6900209675995</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>19.7</v>
+        <v>134</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>19.18294358768184</v>
+        <v>45.72880123093304</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.04839134684389</v>
+        <v>17.68952449603709</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.281843448465084</v>
+        <v>0.5724287018589082</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.6414569057608555</v>
+        <v>0.1397509937340862</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8390</v>
+        <v>8222</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>249.3868574293144</v>
+        <v>352.2405372815024</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>88.7</v>
+        <v>34.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.92355429664446</v>
+        <v>39.29997492848862</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.21974274549402</v>
+        <v>8.649755110528629</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.142384019663946</v>
+        <v>0.9437931420800486</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.094372873613405</v>
+        <v>0.0408884113644458</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8071</v>
+        <v>8092</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>235.3510210693698</v>
+        <v>349.5993453369521</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20.4</v>
+        <v>12.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>35.41842743505548</v>
+        <v>40.49370664895215</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.79408122030791</v>
+        <v>13.7548529002395</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7990916842845613</v>
+        <v>0.2000625868850852</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0765256818389866</v>
+        <v>0.0003949748940002</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8092</v>
+        <v>8080</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>234.599345336952</v>
+        <v>341.3721296644778</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>12.25</v>
+        <v>27.65</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.49370674837681</v>
+        <v>50.87560446146461</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.75485283777848</v>
+        <v>22.25645036266191</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2000625868850852</v>
+        <v>1.037212966447785</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0003949748459311</v>
+        <v>0.3194376937451093</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8072</v>
+        <v>8404</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>232.4912065656047</v>
+        <v>339.3909867300851</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26.1</v>
+        <v>13.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.6544120487404</v>
+        <v>39.61018904126573</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.88344911190796</v>
+        <v>33.31039019531062</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5229623663093425</v>
+        <v>0.9024647111365524</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1564944455954966</v>
+        <v>0.1024435624269132</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>9955</v>
+        <v>8048</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>229.05061698587</v>
+        <v>339.252647025677</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>22.4</v>
+        <v>50.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.08689826841545</v>
+        <v>46.9503559122286</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.32600024808885</v>
+        <v>12.34381173198275</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5182805047671072</v>
+        <v>0.7137473255912051</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.06723184999982031</v>
+        <v>0.0978334095313055</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8404</v>
+        <v>8481</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>224.3909867300851</v>
+        <v>337.5345650301353</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>13.3</v>
+        <v>40.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.6101890307546</v>
+        <v>41.72025893449905</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33.31039016810303</v>
+        <v>17.11942705766468</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9024647111365524</v>
+        <v>1.022120388746455</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1024435624990148</v>
+        <v>-0.0250147772225017</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8048</v>
+        <v>8410</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>224.252647025677</v>
+        <v>336.9768870066974</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>50.6</v>
+        <v>26.95</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46.95035582387847</v>
+        <v>34.80276202191544</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.34381169067358</v>
+        <v>45.96149983797056</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7137473255912051</v>
+        <v>0.09064535734947959</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0978334096394614</v>
+        <v>0.0614875945099704</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8472</v>
+        <v>8131</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>221.7922228221577</v>
+        <v>335.9961182861014</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>54.05239908918664</v>
+        <v>45.36081569769771</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.80296817482278</v>
+        <v>18.33396411807496</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.699474908288777</v>
+        <v>0.6821088216441075</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1386467654637373</v>
+        <v>-0.1249749537145183</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8443</v>
+        <v>8105</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>221.1093246050189</v>
+        <v>332.6628313436526</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.2</v>
+        <v>14.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.81120798507352</v>
+        <v>39.87833727716662</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>39.44493621192312</v>
+        <v>14.45643094848555</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.092845366576031</v>
+        <v>0.4870352971519104</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1302994445676255</v>
+        <v>-0.0476189390285308</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8105</v>
+        <v>8163</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>217.6628313436526</v>
+        <v>328.4287832600474</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14.2</v>
+        <v>28.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.87833714602682</v>
+        <v>34.63367560324035</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.4564309092325</v>
+        <v>17.06778601687029</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4870352971519104</v>
+        <v>1.332735543168389</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0476189390094598</v>
+        <v>-0.1148793890200345</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8085</v>
+        <v>8261</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>216.2008846037744</v>
+        <v>326.9623959051303</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14.2</v>
+        <v>153</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.82588152242911</v>
+        <v>35.525122531037</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.39977397014297</v>
+        <v>17.90673987130176</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6774960452748267</v>
+        <v>0.5853389722790731</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1011007778269784</v>
+        <v>-2.996045250458258</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8341</v>
+        <v>8076</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>214.7700762079758</v>
+        <v>325.7017516855774</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>20.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.57303476459599</v>
+        <v>37.98957980923261</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.49285209817657</v>
+        <v>31.12868360324418</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.969761977587104</v>
+        <v>1.052516938384462</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1085993931909246</v>
+        <v>-0.0247000252079315</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8163</v>
+        <v>8932</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>213.4287832600473</v>
+        <v>312.8728575111327</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>28.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>34.63367549722796</v>
+        <v>40.06776077859649</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.06778597966165</v>
+        <v>15.5695394459199</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.332735543168389</v>
+        <v>0.8844844895698253</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.114879389056087</v>
+        <v>0.0488160101509649</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8222</v>
+        <v>8487</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>212.2405372815024</v>
+        <v>307.4937706717179</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>34.55</v>
+        <v>68.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.29997456375673</v>
+        <v>31.55069229039728</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.649755089502083</v>
+        <v>13.58617829035659</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9437931420800486</v>
+        <v>0.7928547064694216</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0408884114846187</v>
+        <v>-0.1273480257011608</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8080</v>
+        <v>8121</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>201.3721296644779</v>
+        <v>305.4277344949405</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>27.65</v>
+        <v>30.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.87560523256595</v>
+        <v>46.94950996685714</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.25645523858485</v>
+        <v>29.3401331134887</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.037212966447785</v>
+        <v>0.3322463420473356</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,11 +6029,11 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3194376868111255</v>
+        <v>-0.2380532472857123</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>190.1773101681888</v>
+        <v>305.1773101681901</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>37.9</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.54677830908594</v>
+        <v>35.54677840204556</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.13276397614634</v>
+        <v>20.1327640039679</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.16284761842382</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.036497419138291</v>
+        <v>0.0364974190061007</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8067</v>
+        <v>8411</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>187.5367504912284</v>
+        <v>283.1774944922904</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0</v>
+        <v>11.15</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>8.200736060017235</v>
+        <v>22.66303678042379</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.57400721344743</v>
+        <v>45.90028044845501</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0</v>
+        <v>0.4483031683734808</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.7372716777983569</v>
+        <v>-0.0527370381886794</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8076</v>
+        <v>8374</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>185.7017516855765</v>
+        <v>279.8978557916806</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20.7</v>
+        <v>70.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.98957978483661</v>
+        <v>30.94204802118448</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.12868361581904</v>
+        <v>17.12229819844519</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.052516938384462</v>
+        <v>0.9961367137377904</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0247000251959136</v>
+        <v>-0.4197808017904412</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8054</v>
+        <v>8478</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>181.6451946410396</v>
+        <v>272.1890912424388</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>138.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>32.81728592189532</v>
+        <v>40.47587135641839</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.76329733697455</v>
+        <v>12.2367905079872</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8362700226787256</v>
+        <v>1.573281480373512</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.296795008837767</v>
+        <v>-0.0140575488263234</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8104</v>
+        <v>8291</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>180.910924227246</v>
+        <v>250.5490675627793</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>29.5</v>
+        <v>19.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.27184882429297</v>
+        <v>19.18294358768184</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.57769446952199</v>
+        <v>15.04839134684389</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5972346470198393</v>
+        <v>1.281843448465084</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1593651362207177</v>
+        <v>-0.6414569057608555</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8481</v>
+        <v>9136</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>167.5345650301355</v>
+        <v>246.0249547191637</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>40.3</v>
+        <v>8.75</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.72025893449905</v>
+        <v>26.46183465443188</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.11942704740101</v>
+        <v>17.09887048578367</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.022120388746455</v>
+        <v>0.6335601087264933</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0250147772225017</v>
+        <v>0.0233638704479001</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8487</v>
+        <v>8071</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>167.4937706717179</v>
+        <v>235.3510210693712</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>68.3</v>
+        <v>20.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>31.55069233019196</v>
+        <v>35.41842741187915</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.58617829035659</v>
+        <v>15.79408126862023</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7928547064694216</v>
+        <v>0.7990916842845613</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1273480257251986</v>
+        <v>-0.0765256818870549</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8410</v>
+        <v>9955</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>166.9768870066974</v>
+        <v>229.0506169858758</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>26.95</v>
+        <v>22.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.80276159831048</v>
+        <v>36.08689832585588</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>45.96149989083099</v>
+        <v>13.32600023689257</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.09064535734947959</v>
+        <v>0.5182805047671072</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0614875945099704</v>
+        <v>-0.06723184995174949</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8499</v>
+        <v>8067</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>155.4762402757163</v>
+        <v>187.5367504912284</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.08597286004429</v>
+        <v>8.200736031038886</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>6.818493748138487</v>
+        <v>23.57400721516769</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.118539051035382</v>
+        <v>0</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.328752706292778</v>
+        <v>-0.7372716777502872</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8478</v>
+        <v>8054</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>132.1890912424389</v>
+        <v>181.6451946410388</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>138.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.47587062753716</v>
+        <v>32.81728589891733</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.23679047170275</v>
+        <v>18.76329738885359</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.573281480373512</v>
+        <v>0.8362700226787256</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0140575481052677</v>
+        <v>-1.296795008597426</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>9136</v>
+        <v>8104</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>131.0249547191637</v>
+        <v>180.910924227246</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>8.75</v>
+        <v>29.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>26.46183465188132</v>
+        <v>37.27184905921021</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.09887039045618</v>
+        <v>14.57769447149603</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6335601087264933</v>
+        <v>0.5972346470198393</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,9 +6612,62 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0233638704503025</v>
+        <v>-0.1593651362086974</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>鼎炫-KY</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>155.4762402757166</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>45.08597302247168</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>6.818493779967932</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.118539051035382</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-1.328752706412937</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
